--- a/etf_holdings/2026-08-28_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:43</t>
+          <t>2026-08-28 06:33:09</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:44</t>
+          <t>2026-08-28 06:33:10</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:45</t>
+          <t>2026-08-28 06:33:11</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:47</t>
+          <t>2026-08-28 06:33:13</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:47</t>
+          <t>2026-08-28 06:33:13</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:47</t>
+          <t>2026-08-28 06:33:13</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:47</t>
+          <t>2026-08-28 06:33:13</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:14:47</t>
+          <t>2026-08-28 06:33:13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:09</t>
+          <t>2026-08-28 06:58:48</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:10</t>
+          <t>2026-08-28 06:58:50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:11</t>
+          <t>2026-08-28 06:58:51</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:13</t>
+          <t>2026-08-28 06:58:52</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:13</t>
+          <t>2026-08-28 06:58:52</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:13</t>
+          <t>2026-08-28 06:58:52</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:13</t>
+          <t>2026-08-28 06:58:52</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:33:13</t>
+          <t>2026-08-28 06:58:52</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.21%2410</t>
+          <t>+0.41%2420</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2410</v>
+        <v>2420</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13.64%588,000</t>
+          <t>13.48%588,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.64%</t>
+          <t>13.48%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.85%345</t>
+          <t>+1.16%349</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>+1.16%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.89%1,448,000</t>
+          <t>4.75%1,448,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>4.75%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,25 +631,25 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+0.5%101.5</t>
+          <t>-0.99%100.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>-0.99%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.72%3,832,000</t>
+          <t>3.70%3,832,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.72%</t>
+          <t>3.70%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,12 +692,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-0.37%135.5</t>
+          <t>0%135.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.37%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H5" t="n">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.70%2,828,000</t>
+          <t>3.65%2,828,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+0.44%6815</t>
+          <t>+5.65%7200</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+0.44%</t>
+          <t>+5.65%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>6815</v>
+        <v>7200</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3.46%53,000</t>
+          <t>3.44%53,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.44%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+3.53%3370</t>
+          <t>-1.93%3305</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3370</v>
+        <v>3305</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.60%83,000</t>
+          <t>2.66%83,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.60%</t>
+          <t>2.66%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+3.38%2450</t>
+          <t>-6.12%2300</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+3.38%</t>
+          <t>-6.12%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>2450</v>
+        <v>2300</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.46%108,000</t>
+          <t>2.52%108,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.52%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.16%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+1.7%2090</t>
+          <t>+1.67%2125</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+1.7%</t>
+          <t>+1.67%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2090</v>
+        <v>2125</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.45%124,000</t>
+          <t>2.47%124,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.45%</t>
+          <t>2.47%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+2.8%73.4</t>
+          <t>-1.09%72.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+2.8%</t>
+          <t>-1.09%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>73.40000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.38%3,473,000</t>
+          <t>2.43%3,473,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.38%</t>
+          <t>2.43%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+10%445.5</t>
+          <t>-1.46%439</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>445.5</v>
+        <v>439</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.15%552,000</t>
+          <t>2.34%552,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.20%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6446藥華醫藥</t>
+          <t>3017奇鋐科技</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.58%1560</t>
+          <t>+0.6%3360</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.58%</t>
+          <t>+0.6%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1560</v>
+        <v>3360</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.10%138,000</t>
+          <t>2.16%68,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.10%</t>
+          <t>2.16%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>138000</v>
+        <v>68000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3017奇鋐科技</t>
+          <t>6187萬潤科技</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+5.86%3340</t>
+          <t>-4.55%1365</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+5.86%</t>
+          <t>-4.55%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>3340</v>
+        <v>1365</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.06%68,000</t>
+          <t>2.05%151,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.06%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>68000</v>
+        <v>151000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2027大成不銹鋼工業</t>
+          <t>6446藥華醫藥</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-2.7%48.65</t>
+          <t>-0.96%1545</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-0.96%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>48.65</v>
+        <v>1545</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.01%4,181,000</t>
+          <t>2.05%138,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.01%</t>
+          <t>2.05%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>4181000</v>
+        <v>138000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,25 +1302,25 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+3.35%555</t>
+          <t>+7.57%597</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+3.35%</t>
+          <t>+7.57%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>555</v>
+        <v>597</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.98%383,000</t>
+          <t>2.02%383,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.02%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:48</t>
+          <t>2026-08-28 15:44:06</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3711日月光投資控股</t>
+          <t>2027大成不銹鋼工業</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+2.2%605</t>
+          <t>-0.51%48.4</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+2.2%</t>
+          <t>-0.51%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>605</v>
+        <v>48.4</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.91%335,000</t>
+          <t>1.94%4,181,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.91%</t>
+          <t>1.94%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>335000</v>
+        <v>4181000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2454聯發科技</t>
+          <t>3711日月光投資控股</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.03%3865</t>
+          <t>+2.64%621</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.03%</t>
+          <t>+2.64%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>3865</v>
+        <v>621</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.90%50,000</t>
+          <t>1.93%335,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.93%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>50000</v>
+        <v>335000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>6187萬潤科技</t>
+          <t>7769鴻勁精密</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+10%1430</t>
+          <t>+2.29%6490</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>+2.29%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>1430</v>
+        <v>6490</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.89%151,000</t>
+          <t>1.87%31,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>151000</v>
+        <v>31000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>7769鴻勁精密</t>
+          <t>2454聯發科技</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+0.16%6345</t>
+          <t>+3.1%3985</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>+3.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6345</v>
+        <v>3985</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.89%31,000</t>
+          <t>1.84%50,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>1.84%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>31000</v>
+        <v>50000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2383台光電子材料</t>
+          <t>3037欣興電子</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-6.7%5500</t>
+          <t>-5.93%1110</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>-5.93%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>5500</v>
+        <v>1110</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.81%32,000</t>
+          <t>1.80%160,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.81%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>32000</v>
+        <v>160000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>3037欣興電子</t>
+          <t>2610中華航空</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+1.72%1180</t>
+          <t>-2.16%20.35</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-2.16%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>1180</v>
+        <v>20.35</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.78%160,000</t>
+          <t>1.74%8,783,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.74%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>160000</v>
+        <v>8783000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2610中華航空</t>
+          <t>2383台光電子材料</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0%20.8</t>
+          <t>0%5490</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1738,20 +1738,20 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>20.8</v>
+        <v>5490</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.76%8,783,000</t>
+          <t>1.67%32,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.76%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>8783000</v>
+        <v>32000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>6442光紅建聖</t>
+          <t>2603長榮海運</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.93%1595</t>
+          <t>-0.43%231.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.93%</t>
+          <t>-0.43%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1595</v>
+        <v>231.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.64%106,000</t>
+          <t>1.61%726,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.64%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>106000</v>
+        <v>726000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,25 +1846,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2603長榮海運</t>
+          <t>6442光紅建聖</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+0.65%232.5</t>
+          <t>+1.25%1615</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+0.65%</t>
+          <t>+1.25%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>232.5</v>
+        <v>1615</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.61%726,000</t>
+          <t>1.61%106,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1873,11 +1873,11 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>726000</v>
+        <v>106000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2059川湖科技</t>
+          <t>3008大立光電</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0%14340</t>
+          <t>+2.17%7065</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.17%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>14340</v>
+        <v>7065</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.53%11,000</t>
+          <t>1.58%24,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.58%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3661世芯電子</t>
+          <t>1301台灣塑膠工業</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.27%3870</t>
+          <t>-0.63%62.7</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.27%</t>
+          <t>-0.63%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>3870</v>
+        <v>62.7</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.52%40,000</t>
+          <t>1.57%2,612,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.52%</t>
+          <t>1.57%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>40000</v>
+        <v>2612000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1301台灣塑膠工業</t>
+          <t>2059川湖科技</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+4.99%63.1</t>
+          <t>-0.28%14300</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+4.99%</t>
+          <t>-0.28%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>63.1</v>
+        <v>14300</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.51%2,612,000</t>
+          <t>1.50%11,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.50%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2612000</v>
+        <v>11000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3653健策精密工業</t>
+          <t>3661世芯電子</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-1.4%5645</t>
+          <t>+5.04%4065</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>+5.04%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>5645</v>
+        <v>4065</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.49%27,000</t>
+          <t>1.47%40,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.49%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>27000</v>
+        <v>40000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,25 +2151,25 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3008大立光電</t>
+          <t>3653健策精密工業</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+9.94%6915</t>
+          <t>+2.48%5785</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+2.48%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>6915</v>
+        <v>5785</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.45%24,000</t>
+          <t>1.45%27,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2178,11 +2178,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>24000</v>
+        <v>27000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2308台達電子工業</t>
+          <t>8996高力熱處理工業</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+1.14%1770</t>
+          <t>-3.44%1265</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+1.14%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>1770</v>
+        <v>1265</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.38%82,000</t>
+          <t>1.41%113,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>82000</v>
+        <v>113000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:50</t>
+          <t>2026-08-28 15:44:08</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3036文曄科技</t>
+          <t>2308台達電子工業</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-1.78%193</t>
+          <t>+3.39%1830</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-1.78%</t>
+          <t>+3.39%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>193</v>
+        <v>1830</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.30%686,000</t>
+          <t>1.38%82,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.38%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>686000</v>
+        <v>82000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+1.08%187.5</t>
+          <t>-2.67%182.5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+1.08%</t>
+          <t>-2.67%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>187.5</v>
+        <v>182.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>8996高力熱處理工業</t>
+          <t>3036文曄科技</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+9.62%1310</t>
+          <t>+1.55%196</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+9.62%</t>
+          <t>+1.55%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1310</v>
+        <v>196</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.30%113,000</t>
+          <t>1.26%686,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.26%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>113000</v>
+        <v>686000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.77%77.1</t>
+          <t>-1.82%75.7</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>77.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.24%1,657,000</t>
+          <t>1.22%1,657,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.22%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>2408南亞科技</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.89%675</t>
+          <t>-0.18%540</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.89%</t>
+          <t>-0.18%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>675</v>
+        <v>540</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.97%146,000</t>
+          <t>0.99%193,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>0.99%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>146000</v>
+        <v>193000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2408南亞科技</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+4.64%541</t>
+          <t>-0.89%669</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+4.64%</t>
+          <t>-0.89%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>541</v>
+        <v>669</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.96%193,000</t>
+          <t>0.94%146,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>193000</v>
+        <v>146000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+9.75%1295</t>
+          <t>-4.25%1240</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+9.75%</t>
+          <t>-4.25%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1295</v>
+        <v>1240</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.54%48,000</t>
+          <t>0.59%48,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.54%</t>
+          <t>0.59%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+2.48%186</t>
+          <t>-2.42%181.5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+2.48%</t>
+          <t>-2.42%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>186</v>
+        <v>181.5</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.42%243,000</t>
+          <t>0.43%243,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.43%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+1.41%2155</t>
+          <t>-0.23%2150</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>2155</v>
+        <v>2150</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.2%2490</t>
+          <t>-0.2%2485</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-0.2%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>2490</v>
+        <v>2485</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.29%12,000</t>
+          <t>0.28%12,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+2.17%141.5</t>
+          <t>+1.77%144</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>+1.77%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>141.5</v>
+        <v>144</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.20%154,000</t>
+          <t>0.21%154,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2303聯華電子</t>
+          <t>4958臻鼎科技控股</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-4.05%118.5</t>
+          <t>+0.73%480.5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-4.05%</t>
+          <t>+0.73%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>118.5</v>
+        <v>480.5</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.20%171,000</t>
+          <t>0.21%46,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.21%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>171000</v>
+        <v>46000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4958臻鼎科技控股</t>
+          <t>2891中國信託金融控股</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+5.3%477</t>
+          <t>+0.94%64.4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+5.3%</t>
+          <t>+0.94%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>477</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.20%46,000</t>
+          <t>0.19%306,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.20%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>46000</v>
+        <v>306000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2049上銀科技</t>
+          <t>2368金像電子（股）公司</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+1.84%359.5</t>
+          <t>+9.71%1130</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+1.84%</t>
+          <t>+9.71%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>359.5</v>
+        <v>1130</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.19%55,000</t>
+          <t>0.19%19,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>55000</v>
+        <v>19000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2891中國信託金融控股</t>
+          <t>2049上銀科技</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.24%63.8</t>
+          <t>-1.53%354</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-1.53%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>63.8</v>
+        <v>354</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.19%306,000</t>
+          <t>0.19%55,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>306000</v>
+        <v>55000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:51</t>
+          <t>2026-08-28 15:44:09</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,25 +3188,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2368金像電子（股）公司</t>
+          <t>2303聯華電子</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-0.96%1030</t>
+          <t>+9.7%130</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-0.96%</t>
+          <t>+9.7%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>1030</v>
+        <v>130</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.19%19,000</t>
+          <t>0.19%171,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3215,11 +3215,11 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>19000</v>
+        <v>171000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:52</t>
+          <t>2026-08-28 15:44:10</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,25 +3254,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+2.49%2055</t>
+          <t>+9.98%2260</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+2.49%</t>
+          <t>+9.98%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2055</v>
+        <v>2260</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.17%9,000</t>
+          <t>0.18%9,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.18%</t>
         </is>
       </c>
       <c r="K47" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:52</t>
+          <t>2026-08-28 15:44:10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+2.23%252</t>
+          <t>+0.4%253</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>+0.4%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:52</t>
+          <t>2026-08-28 15:44:10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,25 +3376,25 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+0.51%1990</t>
+          <t>+1.01%2010</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+1.01%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1990</v>
+        <v>2010</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.10%5,000</t>
+          <t>0.09%5,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.10%</t>
+          <t>0.09%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:52</t>
+          <t>2026-08-28 15:44:10</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.95%958</t>
+          <t>+1.46%972</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.95%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>958</v>
+        <v>972</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 06:58:52</t>
+          <t>2026-08-28 15:44:10</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+3.75%914</t>
+          <t>-1.64%899</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+3.75%</t>
+          <t>-1.64%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>914</v>
+        <v>899</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:06</t>
+          <t>2026-08-28 17:25:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:08</t>
+          <t>2026-08-28 17:25:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:09</t>
+          <t>2026-08-28 17:25:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:10</t>
+          <t>2026-08-28 17:25:19</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:10</t>
+          <t>2026-08-28 17:25:19</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:10</t>
+          <t>2026-08-28 17:25:19</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:10</t>
+          <t>2026-08-28 17:25:19</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 15:44:10</t>
+          <t>2026-08-28 17:25:19</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:15</t>
+          <t>2026-08-28 20:38:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:17</t>
+          <t>2026-08-28 20:38:32</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:18</t>
+          <t>2026-08-28 20:38:33</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:19</t>
+          <t>2026-08-28 20:38:34</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:19</t>
+          <t>2026-08-28 20:38:34</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:19</t>
+          <t>2026-08-28 20:38:34</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:19</t>
+          <t>2026-08-28 20:38:34</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 17:25:19</t>
+          <t>2026-08-28 20:38:34</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:30</t>
+          <t>2026-08-28 21:41:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:32</t>
+          <t>2026-08-28 21:41:23</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:33</t>
+          <t>2026-08-28 21:41:24</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:34</t>
+          <t>2026-08-28 21:41:26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:34</t>
+          <t>2026-08-28 21:41:26</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:34</t>
+          <t>2026-08-28 21:41:26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:34</t>
+          <t>2026-08-28 21:41:26</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 20:38:34</t>
+          <t>2026-08-28 21:41:26</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-08-28_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-08-28_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:22</t>
+          <t>2026-08-28 21:46:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:23</t>
+          <t>2026-08-28 21:46:44</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:24</t>
+          <t>2026-08-28 21:46:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:26</t>
+          <t>2026-08-28 21:46:46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:26</t>
+          <t>2026-08-28 21:46:46</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:26</t>
+          <t>2026-08-28 21:46:46</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:26</t>
+          <t>2026-08-28 21:46:46</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-08-28 21:41:26</t>
+          <t>2026-08-28 21:46:46</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
